--- a/AI Audit Log_VoTranPhuongUyen.xlsx
+++ b/AI Audit Log_VoTranPhuongUyen.xlsx
@@ -5,16 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\semester 7\SDN302\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\semester 7\SWD392\demo\ai-audit-log-uynpun\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98AD61C3-2621-489C-8CBB-A0A72CB97AA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4346510-3A7F-4751-8A22-84290EEDCD6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
   <sheets>
-    <sheet name="Template" sheetId="1" r:id="rId1"/>
-    <sheet name="Assignment 1" sheetId="2" r:id="rId2"/>
+    <sheet name="Week 2" sheetId="1" r:id="rId1"/>
+    <sheet name="Week 3" sheetId="2" r:id="rId2"/>
     <sheet name="Assignment 2" sheetId="3" r:id="rId3"/>
     <sheet name="Assignment 3" sheetId="4" r:id="rId4"/>
   </sheets>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="39">
   <si>
     <t>Giai đoạn/Thành phần DTC</t>
   </si>
@@ -322,6 +322,432 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Nhóm quyết định dùng Draw.io vì miễn phí, dễ thao tác và hỗ trợ chia sẻ chỉnh sửa trực tuyến thuận tiện.</t>
+    </r>
+  </si>
+  <si>
+    <t>Phản hồi của AI &amp; Quyết định của người học (Reflection)</t>
+  </si>
+  <si>
+    <t>Slot 5</t>
+  </si>
+  <si>
+    <t>"Trong UML Class Diagram, làm thế nào để xác định thuộc tính (attributes) và phương thức (operations) cho mỗi lớp từ tài liệu yêu cầu?"</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI hướng dẫn phân tích danh từ để tìm thuộc tính và động từ để tìm phương thức. Ví dụ lớp Booking có bookingId, bookingDate, status và các phương thức create(), cancel(), update(). </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi rà soát lại từng lớp trong hệ thống và bổ sung các thuộc tính, phương thức còn thiếu để mô hình phản ánh đúng nghiệp vụ.</t>
+    </r>
+  </si>
+  <si>
+    <t>"Làm thế nào để xác định Association, Aggregation và Composition trong UML? Dấu hiệu nhận biết từng loại quan hệ là gì?"</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI giải thích Association dùng khi hai lớp chỉ liên kết với nhau, Aggregation khi một đối tượng chứa đối tượng khác nhưng có thể tồn tại độc lập, Composition khi vòng đời phụ thuộc hoàn toàn. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi xem xét lại các quan hệ trong hệ thống và chọn loại quan hệ phù hợp thay vì chỉ dùng Association cho tất cả các lớp.</t>
+    </r>
+  </si>
+  <si>
+    <t>"Trong UML, khi nào nên sử dụng Interface thay vì lớp cha (Abstract Class)? Hãy so sánh ưu nhược điểm."</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI phân tích Interface phù hợp cho việc định nghĩa hành vi chung, còn Abstract Class phù hợp khi cần chia sẻ thuộc tính hoặc logic xử lý. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi sử dụng Interface cho Repository và Service, đồng thời giữ Abstract Class cho các thực thể có nhiều đặc điểm dùng chung.</t>
+    </r>
+  </si>
+  <si>
+    <t>"Làm thế nào để xác định multiplicity chính xác giữa Customer và Booking trong hệ thống đặt xe?"</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI phân tích rằng một Customer có thể tạo nhiều Booking, nhưng mỗi Booking chỉ thuộc về một Customer, do đó multiplicity là 1 ↔ 0..*. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi bổ sung multiplicity vào sơ đồ để thể hiện rõ ràng quy tắc nghiệp vụ và tránh hiểu nhầm trong quá trình triển khai.</t>
+    </r>
+  </si>
+  <si>
+    <t>"Có nên đưa các lớp DTO (Data Transfer Object) vào UML Class Diagram hay không? Vì sao?"</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI cho biết nếu sơ đồ nhằm mô tả domain model thì không cần DTO. Nếu sơ đồ thiết kế chi tiết hệ thống hoặc API thì nên bổ sung DTO để thể hiện luồng trao đổi dữ liệu. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi chỉ giữ Entity trong sơ đồ nghiệp vụ và tách DTO sang sơ đồ thiết kế chi tiết để tránh làm sơ đồ quá phức tạp.</t>
+    </r>
+  </si>
+  <si>
+    <t>"Trong mô hình Repository Pattern, Class Diagram nên thể hiện Generic Repository như thế nào?"</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI hướng dẫn tạo interface IGenericRepository chứa các thao tác CRUD cơ bản, sau đó các repository cụ thể kế thừa hoặc triển khai interface này. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi thêm IGenericRepository vào sơ đồ và sử dụng quan hệ Realization để các repository cụ thể triển khai interface đó.</t>
+    </r>
+  </si>
+  <si>
+    <t>"Làm thế nào để biểu diễn Design Pattern MVC trong UML Class Diagram?"</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI đề xuất chia các lớp thành ba nhóm Model, View và Controller; Controller tương tác với Service và Model, View chỉ giao tiếp với Controller. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi nhóm các lớp theo kiến trúc MVC để người đọc dễ hiểu cấu trúc hệ thống hơn.</t>
+    </r>
+  </si>
+  <si>
+    <t>"Khi thiết kế Class Diagram, có nên thể hiện đầy đủ getter/setter hay chỉ tập trung vào nghiệp vụ chính?"</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI cho biết trong sơ đồ phân tích thường không cần hiển thị getter/setter để tránh rối. Chỉ nên thể hiện các phương thức nghiệp vụ quan trọng. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi lược bỏ getter/setter và giữ lại các chức năng chính để sơ đồ ngắn gọn, dễ đọc hơn.</t>
+    </r>
+  </si>
+  <si>
+    <t>"Làm thế nào để xác định các lớp Service cần có trong hệ thống từ tài liệu yêu cầu?"</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI hướng dẫn nhóm các chức năng nghiệp vụ liên quan thành một Service. Ví dụ BookingService quản lý đặt xe, PaymentService xử lý thanh toán. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi tạo các Service dựa trên từng nhóm nghiệp vụ chính thay vì tạo quá nhiều Service nhỏ lẻ.</t>
+    </r>
+  </si>
+  <si>
+    <t>"Trong UML, Dependency khác gì với Association? Khi nào nên sử dụng mỗi loại?"</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI giải thích Association biểu thị mối quan hệ lâu dài giữa các đối tượng, còn Dependency chỉ thể hiện sự phụ thuộc tạm thời khi sử dụng. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi thay một số Association bằng Dependency để phản ánh chính xác mức độ liên kết giữa các lớp trong hệ thống.</t>
     </r>
   </si>
 </sst>
@@ -839,9 +1265,170 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59E3EFE9-6FFB-49CC-BE69-0C0E36C6253E}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="112.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
